--- a/force-app/main/default/documents/Loop__LOOP_Files/CACFADCEAa97e44167ce948a682f9f4c68f64df87.xlsx
+++ b/force-app/main/default/documents/Loop__LOOP_Files/CACFADCEAa97e44167ce948a682f9f4c68f64df87.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RohitBilgi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RohitBilgi\Desktop\Files\Leaseworks\Carlyle\Tech Spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3FA336-C4F7-479E-B3B9-925E7A353F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C75788F-C2DF-4FDA-BF6B-83166645C275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" tabRatio="645" firstSheet="1" activeTab="1" xr2:uid="{BFBE8F3F-363D-4434-AB03-6A024B23687E}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" tabRatio="645" xr2:uid="{BFBE8F3F-363D-4434-AB03-6A024B23687E}"/>
   </bookViews>
   <sheets>
     <sheet name="SalesforceData" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <definedName name="Spec_Mass_and_Balance_Unit">SalesforceData!$C$2</definedName>
     <definedName name="Spec_Mass_and_Balance_Unit_Alt">SalesforceData!$E$2</definedName>
     <definedName name="Spec_Mass_and_Balance_Weight">SalesforceData!$D$2</definedName>
-    <definedName name="Spec_Mass_and_Balance_Weight_Alt">SalesforceData!$F$2</definedName>
+    <definedName name="Spec_Mass_and_Balance_Weight_Alternative_manual_entry">SalesforceData!$F$2</definedName>
     <definedName name="Spec_Mass_and_Balance_Weight_Type">SalesforceData!$A$2</definedName>
     <definedName name="Weight_Table_Data">'Final Preview Data'!$A$4:$I$50</definedName>
     <definedName name="WeightAltUnit_1">'Final Data'!$C$4</definedName>
